--- a/docs/ig/ValueSet-dipag-dokument-artderarchivierung-vs.xlsx
+++ b/docs/ig/ValueSet-dipag-dokument-artderarchivierung-vs.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet für die Differenzierung von verschiedenen Arten von Markierungen eines Dokumentes</t>
+    <t>ValueSet für die Angabe der Art der Archivierung eines Dokumentes (ePA oder persönliche Ablage)</t>
   </si>
   <si>
     <t>Purpose</t>
